--- a/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-1,01; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,4</t>
+          <t>-0,74; 0,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; -0,11</t>
+          <t>-1,17; -0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,69</t>
+          <t>-0,7; 0,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; -0,14</t>
+          <t>-0,93; -0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,35</t>
+          <t>-0,56; 0,39</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,25; 305,81</t>
+          <t>-87,34; 277,04</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,0</t>
+          <t>-0,65; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,43</t>
+          <t>-0,35; 0,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; -0,07</t>
+          <t>-0,75; -0,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,47</t>
+          <t>-0,47; 0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; -0,08</t>
+          <t>-0,53; -0,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,31</t>
+          <t>-0,26; 0,32</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,0; 374,78</t>
+          <t>-79,98; 392,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,0</t>
+          <t>-1,03; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,38</t>
+          <t>-0,73; 0,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,11</t>
+          <t>-1,1; -0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,8</t>
+          <t>-0,65; 0,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; -0,14</t>
+          <t>-0,86; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,39</t>
+          <t>-0,54; 0,38</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,34; 277,04</t>
+          <t>-100,0; 333,6</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,0</t>
+          <t>-0,71; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,43</t>
+          <t>-0,4; 0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; -0,07</t>
+          <t>-0,77; -0,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,42</t>
+          <t>-0,45; 0,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; -0,09</t>
+          <t>-0,52; -0,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,32</t>
+          <t>-0,26; 0,34</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,98; 392,18</t>
+          <t>-77,88; 505,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,98</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,07</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,0</t>
+          <t>-1,09; -0,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,46</t>
+          <t>-0,66; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,11</t>
+          <t>-1,14; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,67</t>
+          <t>-0,73; 0,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; -0,13</t>
+          <t>-0,83; -0,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,38</t>
+          <t>-0,5; 0,35</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>-14,94%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-20,36%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-14,94%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 333,6</t>
+          <t>-86,25; 305,81</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>-0,73; -0,07</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-0,42; 0,47</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>-0,71; 0,0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,44</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; -0,07</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,45</t>
+          <t>-0,37; 0,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; -0,05</t>
+          <t>-0,54; -0,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,34</t>
+          <t>-0,27; 0,31</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>-15,52%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>28,43%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-15,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 505,22</t>
+          <t>-81,0; 374,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,255 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.981612263140641</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.4553905503205299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,08</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,3</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>5.083475696528185</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>2.29999029177005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; -0,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 0,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,14; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 0,4</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,83; -0,14</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 0,35</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-14,94%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-20,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-17,75%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.4031381326548411</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.06023399280165507</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3301035366414033</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.06722207270290172</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.3691111241947116</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.06553365653363172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-86,25; 305,81</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.09347568876873</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.6633020901616332</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.140217239745098</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.7272973571410918</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.833058715014816</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.4985051857181276</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-0.1101268155943153</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6885994371340769</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.3994944334730369</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.1395577105264661</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.3492025179295177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.149412789122646</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2036393592957052</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1775445177291967</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.862477001704214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>3.058147935890311</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +856,237 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; -0,07</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,42; 0,47</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,71; 0,0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,37; 0,43</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; -0,08</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,27; 0,31</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-15,52%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-81,0; 374,78</t>
-        </is>
-      </c>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.2663437755522588</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.04134467241679526</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.2016853338466997</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.05733002146791469</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.2349582251469164</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.006574009393322134</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7263827973268335</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.4155194182909795</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.7080375095689969</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.3659377353164698</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.5384911446558771</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.2686223727779254</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-0.07251451417011628</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.4721237713637388</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.4304967221337429</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.08426276064928284</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.3071468387668007</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1552304810993531</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.2842547862775736</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.02797948183857572</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="n">
+        <v>-0.8100226754122223</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="n">
+        <v>3.747792459217052</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1094,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
